--- a/esyluban/examples/release/DataTables/test/inline_defs.xlsx
+++ b/esyluban/examples/release/DataTables/test/inline_defs.xlsx
@@ -591,7 +591,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="H2:L2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -834,7 +834,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="J2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
